--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -675,7 +675,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Phan Như Ngọc</v>
+        <v>Phan Hiền Phúc Đạt</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -797,7 +797,7 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>Phan Hiền Phúc Đạt</v>
+        <v>Nguyễn Phương Linh</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -908,256 +908,12 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v>Nguyễn Phạm Quỳnh Trang</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str">
-        <v/>
-      </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-      <c r="U14" t="str">
-        <v/>
-      </c>
-      <c r="V14" t="str">
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <v/>
-      </c>
-      <c r="X14" t="str">
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <v/>
-      </c>
-      <c r="Z14" t="str">
-        <v/>
-      </c>
-      <c r="AA14" t="str">
-        <v/>
-      </c>
-      <c r="AB14" t="str">
-        <v/>
-      </c>
-      <c r="AC14" t="str">
-        <v/>
-      </c>
-      <c r="AD14" t="str">
-        <v/>
-      </c>
-      <c r="AE14" t="str">
-        <v/>
-      </c>
-      <c r="AF14" t="str">
-        <v/>
-      </c>
-      <c r="AG14" t="str">
-        <v/>
-      </c>
-      <c r="AH14" t="str">
-        <v/>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>Nguyễn Phương Linh</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <v/>
-      </c>
-      <c r="V15" t="str">
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <v/>
-      </c>
-      <c r="X15" t="str">
-        <v/>
-      </c>
-      <c r="Y15" t="str">
-        <v/>
-      </c>
-      <c r="Z15" t="str">
-        <v/>
-      </c>
-      <c r="AA15" t="str">
-        <v/>
-      </c>
-      <c r="AB15" t="str">
-        <v/>
-      </c>
-      <c r="AC15" t="str">
-        <v/>
-      </c>
-      <c r="AD15" t="str">
-        <v/>
-      </c>
-      <c r="AE15" t="str">
-        <v/>
-      </c>
-      <c r="AF15" t="str">
-        <v/>
-      </c>
-      <c r="AG15" t="str">
-        <v/>
-      </c>
-      <c r="AH15" t="str">
-        <v/>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -675,7 +675,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Phan Hiền Phúc Đạt</v>
+        <v>Nguyễn Phương Linh</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -786,134 +786,12 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v>Nguyễn Phương Linh</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v/>
-      </c>
-      <c r="S13" t="str">
-        <v/>
-      </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-      <c r="U13" t="str">
-        <v/>
-      </c>
-      <c r="V13" t="str">
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <v/>
-      </c>
-      <c r="X13" t="str">
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <v/>
-      </c>
-      <c r="Z13" t="str">
-        <v/>
-      </c>
-      <c r="AA13" t="str">
-        <v/>
-      </c>
-      <c r="AB13" t="str">
-        <v/>
-      </c>
-      <c r="AC13" t="str">
-        <v/>
-      </c>
-      <c r="AD13" t="str">
-        <v/>
-      </c>
-      <c r="AE13" t="str">
-        <v/>
-      </c>
-      <c r="AF13" t="str">
-        <v/>
-      </c>
-      <c r="AG13" t="str">
-        <v/>
-      </c>
-      <c r="AH13" t="str">
-        <v/>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -675,7 +675,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Nguyễn Phương Linh</v>
+        <v>Phan Hiền Phúc Đạt</v>
       </c>
       <c r="D12" t="str">
         <v/>

--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2987,13 +2987,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>DSP PQC</v>
+        <v/>
       </c>
       <c r="B31" t="str">
-        <v>41863</v>
+        <v>43311</v>
       </c>
       <c r="C31" t="str">
-        <v>Lê Ngọc Thành Tài</v>
+        <v>Đinh Minh Trí</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -3112,10 +3112,10 @@
         <v/>
       </c>
       <c r="B32" t="str">
-        <v>41865</v>
+        <v>43315</v>
       </c>
       <c r="C32" t="str">
-        <v>Nguyễn Đức Lộc</v>
+        <v>Huỳnh Tấn Phước</v>
       </c>
       <c r="D32" t="str">
         <v>M</v>
@@ -3234,10 +3234,10 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>41867</v>
+        <v>43337</v>
       </c>
       <c r="C33" t="str">
-        <v>Phan Thành Nghĩa</v>
+        <v>Vũ Trọng Khánh</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -3348,12 +3348,500 @@
         <v>0</v>
       </c>
       <c r="AN33">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <v>43313</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Cù Trường Phú</v>
+      </c>
+      <c r="D34" t="str">
+        <v>E</v>
+      </c>
+      <c r="E34" t="str">
+        <v>E</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>E</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>M</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>M</v>
+      </c>
+      <c r="L34" t="str">
+        <v>E</v>
+      </c>
+      <c r="M34" t="str">
+        <v>E</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>M</v>
+      </c>
+      <c r="P34" t="str">
+        <v>HC</v>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <v>M</v>
+      </c>
+      <c r="U34" t="str">
+        <v>E</v>
+      </c>
+      <c r="V34" t="str">
+        <v>E</v>
+      </c>
+      <c r="W34" t="str">
+        <v/>
+      </c>
+      <c r="X34" t="str">
+        <v>M</v>
+      </c>
+      <c r="Y34" t="str">
+        <v/>
+      </c>
+      <c r="Z34" t="str">
+        <v/>
+      </c>
+      <c r="AA34" t="str">
+        <v/>
+      </c>
+      <c r="AB34" t="str">
+        <v/>
+      </c>
+      <c r="AC34" t="str">
+        <v>M</v>
+      </c>
+      <c r="AD34" t="str">
+        <v>E</v>
+      </c>
+      <c r="AE34" t="str">
+        <v/>
+      </c>
+      <c r="AF34" t="str">
+        <v>M</v>
+      </c>
+      <c r="AG34" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH34" t="str">
+        <v>M</v>
+      </c>
+      <c r="AI34">
+        <v>1</v>
+      </c>
+      <c r="AJ34">
+        <v>8</v>
+      </c>
+      <c r="AK34">
+        <v>8</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>1</v>
+      </c>
+      <c r="AN34">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>DSP PQC</v>
+      </c>
+      <c r="B35" t="str">
+        <v>41863</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Lê Ngọc Thành Tài</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="L35" t="str">
+        <v>E</v>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="O35" t="str">
+        <v>E</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="R35" t="str">
+        <v>E</v>
+      </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="U35" t="str">
+        <v>M</v>
+      </c>
+      <c r="V35" t="str">
+        <v/>
+      </c>
+      <c r="W35" t="str">
+        <v/>
+      </c>
+      <c r="X35" t="str">
+        <v/>
+      </c>
+      <c r="Y35" t="str">
+        <v/>
+      </c>
+      <c r="Z35" t="str">
+        <v>E</v>
+      </c>
+      <c r="AA35" t="str">
+        <v/>
+      </c>
+      <c r="AB35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AC35" t="str">
+        <v>E</v>
+      </c>
+      <c r="AD35" t="str">
+        <v/>
+      </c>
+      <c r="AE35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AF35" t="str">
+        <v>E</v>
+      </c>
+      <c r="AG35" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH35" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>6</v>
+      </c>
+      <c r="AL35">
+        <v>10</v>
+      </c>
+      <c r="AM35">
+        <v>1</v>
+      </c>
+      <c r="AN35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
+      <c r="B36" t="str">
+        <v>41865</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Nguyễn Đức Lộc</v>
+      </c>
+      <c r="D36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="E36" t="str">
+        <v>E</v>
+      </c>
+      <c r="F36" t="str">
+        <v>E</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>E</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="P36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="S36" t="str">
+        <v>E</v>
+      </c>
+      <c r="T36" t="str">
+        <v/>
+      </c>
+      <c r="U36" t="str">
+        <v>E</v>
+      </c>
+      <c r="V36" t="str">
+        <v/>
+      </c>
+      <c r="W36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="X36" t="str">
+        <v/>
+      </c>
+      <c r="Y36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="Z36" t="str">
+        <v/>
+      </c>
+      <c r="AA36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AB36" t="str">
+        <v>E</v>
+      </c>
+      <c r="AC36" t="str">
+        <v/>
+      </c>
+      <c r="AD36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AE36" t="str">
+        <v>E</v>
+      </c>
+      <c r="AF36" t="str">
+        <v/>
+      </c>
+      <c r="AG36" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AH36" t="str">
+        <v>E</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>8</v>
+      </c>
+      <c r="AL36">
+        <v>10</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v>41867</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Phan Thành Nghĩa</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>M</v>
+      </c>
+      <c r="F37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v>SN</v>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v>E</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>E</v>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="T37" t="str">
+        <v>E</v>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
+      <c r="V37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="W37" t="str">
+        <v/>
+      </c>
+      <c r="X37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="Y37" t="str">
+        <v/>
+      </c>
+      <c r="Z37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AA37" t="str">
+        <v>E</v>
+      </c>
+      <c r="AB37" t="str">
+        <v/>
+      </c>
+      <c r="AC37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AD37" t="str">
+        <v>E</v>
+      </c>
+      <c r="AE37" t="str">
+        <v/>
+      </c>
+      <c r="AF37" t="str">
+        <v>C9</v>
+      </c>
+      <c r="AG37" t="str">
+        <v>E</v>
+      </c>
+      <c r="AH37" t="str">
+        <v/>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>1</v>
+      </c>
+      <c r="AK37">
+        <v>6</v>
+      </c>
+      <c r="AL37">
+        <v>10</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
         <v>212</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN37"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -3731,13 +3731,13 @@
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>M</v>
+        <v>HC</v>
       </c>
       <c r="F37" t="str">
         <v>C9</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>HC</v>
       </c>
       <c r="H37" t="str">
         <v>C9</v>
@@ -3821,10 +3821,10 @@
         <v/>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37">
         <v>6</v>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="AN37">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -3568,7 +3568,7 @@
         <v>C9</v>
       </c>
       <c r="AF35" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AG35" t="str">
         <v>NL</v>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL35">
         <v>10</v>
@@ -3812,7 +3812,7 @@
         <v/>
       </c>
       <c r="AF37" t="str">
-        <v>C9</v>
+        <v>E</v>
       </c>
       <c r="AG37" t="str">
         <v>E</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="AK37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM37">
         <v>0</v>

--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3839,9 +3839,863 @@
         <v>216</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>BRF SGN</v>
+      </c>
+      <c r="B38" t="str">
+        <v>32117</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Lê Song Huyền Vi</v>
+      </c>
+      <c r="D38" t="str">
+        <v>SS</v>
+      </c>
+      <c r="E38" t="str">
+        <v>SS</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="H38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>SS</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v>NC</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="S38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="T38" t="str">
+        <v/>
+      </c>
+      <c r="U38" t="str">
+        <v>PT</v>
+      </c>
+      <c r="V38" t="str">
+        <v>PT</v>
+      </c>
+      <c r="W38" t="str">
+        <v>PT</v>
+      </c>
+      <c r="X38" t="str">
+        <v/>
+      </c>
+      <c r="Y38" t="str">
+        <v>PS</v>
+      </c>
+      <c r="Z38" t="str">
+        <v/>
+      </c>
+      <c r="AA38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AB38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AC38" t="str">
+        <v/>
+      </c>
+      <c r="AD38" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AE38" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AF38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AG38" t="str">
+        <v>HC</v>
+      </c>
+      <c r="AH38" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AI38">
+        <v>1</v>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v/>
+      </c>
+      <c r="B39" t="str">
+        <v>32115</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Đoàn Văn Tây</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="H39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="M39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="N39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="R39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
+      <c r="T39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="U39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="V39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="W39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="X39" t="str">
+        <v/>
+      </c>
+      <c r="Y39" t="str">
+        <v/>
+      </c>
+      <c r="Z39" t="str">
+        <v/>
+      </c>
+      <c r="AA39" t="str">
+        <v/>
+      </c>
+      <c r="AB39" t="str">
+        <v/>
+      </c>
+      <c r="AC39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AD39" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AE39" t="str">
+        <v/>
+      </c>
+      <c r="AF39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AG39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AH39" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
+        <v>31969</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Nguyễn Thị Mỹ Hương</v>
+      </c>
+      <c r="D40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="E40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="F40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="J40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="K40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="O40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="T40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="U40" t="str">
+        <v/>
+      </c>
+      <c r="V40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="W40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="X40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="Y40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="Z40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AA40" t="str">
+        <v/>
+      </c>
+      <c r="AB40" t="str">
+        <v/>
+      </c>
+      <c r="AC40" t="str">
+        <v/>
+      </c>
+      <c r="AD40" t="str">
+        <v/>
+      </c>
+      <c r="AE40" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AF40" t="str">
+        <v/>
+      </c>
+      <c r="AG40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AH40" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v>37388</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Trương Thị Ngọc Loan</v>
+      </c>
+      <c r="D41" t="str">
+        <v>ST</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="J41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="K41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="L41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v>ST</v>
+      </c>
+      <c r="P41" t="str">
+        <v>ST</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>ST</v>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
+      <c r="T41" t="str">
+        <v/>
+      </c>
+      <c r="U41" t="str">
+        <v>ST</v>
+      </c>
+      <c r="V41" t="str">
+        <v/>
+      </c>
+      <c r="W41" t="str">
+        <v/>
+      </c>
+      <c r="X41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="Y41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="Z41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AB41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AC41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AD41" t="str">
+        <v/>
+      </c>
+      <c r="AE41" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AF41" t="str">
+        <v/>
+      </c>
+      <c r="AG41" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AH41" t="str">
+        <v/>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>BRF PQC</v>
+      </c>
+      <c r="B42" t="str">
+        <v>41366</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Phan Như Ngọc</v>
+      </c>
+      <c r="D42" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="E42" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="F42" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="G42" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v>PT</v>
+      </c>
+      <c r="K42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="L42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="R42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="S42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="T42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="U42" t="str">
+        <v/>
+      </c>
+      <c r="V42" t="str">
+        <v>PS</v>
+      </c>
+      <c r="W42" t="str">
+        <v/>
+      </c>
+      <c r="X42" t="str">
+        <v/>
+      </c>
+      <c r="Y42" t="str">
+        <v>PT</v>
+      </c>
+      <c r="Z42" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="AA42" t="str">
+        <v/>
+      </c>
+      <c r="AB42" t="str">
+        <v>PS</v>
+      </c>
+      <c r="AC42" t="str">
+        <v>PT</v>
+      </c>
+      <c r="AD42" t="str">
+        <v>PT</v>
+      </c>
+      <c r="AE42" t="str">
+        <v/>
+      </c>
+      <c r="AF42" t="str">
+        <v>PS</v>
+      </c>
+      <c r="AG42" t="str">
+        <v>PS</v>
+      </c>
+      <c r="AH42" t="str">
+        <v/>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v>41861</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Phan Hiền Phúc Đạt</v>
+      </c>
+      <c r="D43" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="H43" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="I43" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="M43" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="N43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="O43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="P43" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v/>
+      </c>
+      <c r="U43" t="str">
+        <v>PT</v>
+      </c>
+      <c r="V43" t="str">
+        <v/>
+      </c>
+      <c r="W43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="X43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="Y43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="Z43" t="str">
+        <v/>
+      </c>
+      <c r="AA43" t="str">
+        <v>PT</v>
+      </c>
+      <c r="AB43" t="str">
+        <v>PT</v>
+      </c>
+      <c r="AC43" t="str">
+        <v/>
+      </c>
+      <c r="AD43" t="str">
+        <v/>
+      </c>
+      <c r="AE43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="AF43" t="str">
+        <v>PS</v>
+      </c>
+      <c r="AG43" t="str">
+        <v>PT</v>
+      </c>
+      <c r="AH43" t="str">
+        <v>PT</v>
+      </c>
+      <c r="AI43">
+        <v>0</v>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v>42791</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Nguyễn Phương Linh</v>
+      </c>
+      <c r="D44" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="E44" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="I44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="J44" t="str">
+        <v>PS</v>
+      </c>
+      <c r="K44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="N44" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="O44" t="str">
+        <v>PT1</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="R44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="S44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="T44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="U44" t="str">
+        <v>PS</v>
+      </c>
+      <c r="V44" t="str">
+        <v/>
+      </c>
+      <c r="W44" t="str">
+        <v/>
+      </c>
+      <c r="X44" t="str">
+        <v>PT</v>
+      </c>
+      <c r="Y44" t="str">
+        <v/>
+      </c>
+      <c r="Z44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="AA44" t="str">
+        <v>PS</v>
+      </c>
+      <c r="AB44" t="str">
+        <v/>
+      </c>
+      <c r="AC44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="AD44" t="str">
+        <v/>
+      </c>
+      <c r="AE44" t="str">
+        <v/>
+      </c>
+      <c r="AF44" t="str">
+        <v/>
+      </c>
+      <c r="AG44" t="str">
+        <v>HC</v>
+      </c>
+      <c r="AH44" t="str">
+        <v>PS1</v>
+      </c>
+      <c r="AI44">
+        <v>1</v>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CauHinh" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -32,8 +33,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="d"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +66,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,152 +400,1268 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN35"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" customWidth="1"/>
+    <col min="8" max="8" width="5.83203125" customWidth="1"/>
+    <col min="9" max="9" width="5.83203125" customWidth="1"/>
+    <col min="10" max="10" width="5.83203125" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" customWidth="1"/>
+    <col min="13" max="13" width="5.83203125" customWidth="1"/>
+    <col min="14" max="14" width="5.83203125" customWidth="1"/>
+    <col min="15" max="15" width="5.83203125" customWidth="1"/>
+    <col min="16" max="16" width="5.83203125" customWidth="1"/>
+    <col min="17" max="17" width="5.83203125" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" customWidth="1"/>
+    <col min="19" max="19" width="5.83203125" customWidth="1"/>
+    <col min="20" max="20" width="5.83203125" customWidth="1"/>
+    <col min="21" max="21" width="5.83203125" customWidth="1"/>
+    <col min="22" max="22" width="5.83203125" customWidth="1"/>
+    <col min="23" max="23" width="5.83203125" customWidth="1"/>
+    <col min="24" max="24" width="5.83203125" customWidth="1"/>
+    <col min="25" max="25" width="5.83203125" customWidth="1"/>
+    <col min="26" max="26" width="5.83203125" customWidth="1"/>
+    <col min="27" max="27" width="5.83203125" customWidth="1"/>
+    <col min="28" max="28" width="5.83203125" customWidth="1"/>
+    <col min="29" max="29" width="5.83203125" customWidth="1"/>
+    <col min="30" max="30" width="5.83203125" customWidth="1"/>
+    <col min="31" max="31" width="5.83203125" customWidth="1"/>
+    <col min="32" max="32" width="5.83203125" customWidth="1"/>
+    <col min="33" max="33" width="5.83203125" customWidth="1"/>
+    <col min="34" max="34" width="5.83203125" customWidth="1"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1"/>
+    <col min="36" max="36" width="6.83203125" customWidth="1"/>
+    <col min="37" max="37" width="6.83203125" customWidth="1"/>
+    <col min="38" max="38" width="10.83203125" customWidth="1"/>
+    <col min="39" max="39" width="5.83203125" customWidth="1"/>
+    <col min="40" max="40" width="13.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>OCD - IOCC</v>
+        <v>Vị trí trực</v>
       </c>
       <c r="B1" t="str">
-        <v>BẢNG PHÂN CÔNG LỊCH LÀM VIỆC</v>
+        <v>Mã nhân viên</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Họ tên</v>
+      </c>
+      <c r="D1" s="1">
+        <v>46321</v>
+      </c>
+      <c r="E1" s="1">
+        <v>46322</v>
+      </c>
+      <c r="F1" s="1">
+        <v>46323</v>
+      </c>
+      <c r="G1" s="1">
+        <v>46324</v>
+      </c>
+      <c r="H1" s="1">
+        <v>46325</v>
+      </c>
+      <c r="I1" s="1">
+        <v>46326</v>
+      </c>
+      <c r="J1" s="1">
+        <v>46327</v>
+      </c>
+      <c r="K1" s="1">
+        <v>46328</v>
+      </c>
+      <c r="L1" s="1">
+        <v>46329</v>
+      </c>
+      <c r="M1" s="1">
+        <v>46330</v>
+      </c>
+      <c r="N1" s="1">
+        <v>46331</v>
+      </c>
+      <c r="O1" s="1">
+        <v>46332</v>
+      </c>
+      <c r="P1" s="1">
+        <v>46333</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>46334</v>
+      </c>
+      <c r="R1" s="1">
+        <v>46335</v>
+      </c>
+      <c r="S1" s="1">
+        <v>46336</v>
+      </c>
+      <c r="T1" s="1">
+        <v>46337</v>
+      </c>
+      <c r="U1" s="1">
+        <v>46338</v>
+      </c>
+      <c r="V1" s="1">
+        <v>46339</v>
+      </c>
+      <c r="W1" s="1">
+        <v>46340</v>
+      </c>
+      <c r="X1" s="1">
+        <v>46341</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>46342</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>46343</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>46344</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>46345</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>46346</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>46347</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>46348</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>46349</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>46350</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>46351</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>Ca HC</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>Ca M</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>Ca E</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>Ca 9h-21h</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>Tổng giờ công</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>T2</v>
+      </c>
+      <c r="E2" t="str">
+        <v>T3</v>
+      </c>
+      <c r="F2" t="str">
+        <v>T4</v>
+      </c>
+      <c r="G2" t="str">
+        <v>T5</v>
+      </c>
+      <c r="H2" t="str">
+        <v>T6</v>
+      </c>
+      <c r="I2" t="str">
+        <v>T7</v>
+      </c>
+      <c r="J2" t="str">
+        <v>CN</v>
+      </c>
+      <c r="K2" t="str">
+        <v>T2</v>
+      </c>
+      <c r="L2" t="str">
+        <v>T3</v>
+      </c>
+      <c r="M2" t="str">
+        <v>T4</v>
+      </c>
+      <c r="N2" t="str">
+        <v>T5</v>
+      </c>
+      <c r="O2" t="str">
+        <v>T6</v>
+      </c>
+      <c r="P2" t="str">
+        <v>T7</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>CN</v>
+      </c>
+      <c r="R2" t="str">
+        <v>T2</v>
+      </c>
+      <c r="S2" t="str">
+        <v>T3</v>
+      </c>
+      <c r="T2" t="str">
+        <v>T4</v>
+      </c>
+      <c r="U2" t="str">
+        <v>T5</v>
+      </c>
+      <c r="V2" t="str">
+        <v>T6</v>
+      </c>
+      <c r="W2" t="str">
+        <v>T7</v>
+      </c>
+      <c r="X2" t="str">
+        <v>CN</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>T2</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>T3</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>T4</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>T5</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>T6</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>T7</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>CN</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>T2</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>T3</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>T4</v>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
+        <v/>
+      </c>
+      <c r="AL2" t="str">
+        <v/>
+      </c>
+      <c r="AM2" t="str">
+        <v/>
+      </c>
+      <c r="AN2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Duty Manager</v>
+      </c>
+      <c r="B3" t="str">
+        <v>30346</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Đàm Xuân Hiến</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v>E</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>M</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>M</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>E</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>M</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>M</v>
+      </c>
+      <c r="P3" t="str">
+        <v>M</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>E</v>
+      </c>
+      <c r="R3" t="str">
+        <v>E</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v>M</v>
+      </c>
+      <c r="V3" t="str">
+        <v>E</v>
+      </c>
+      <c r="W3" t="str">
+        <v>E</v>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v>M</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v>E</v>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v>M</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>E</v>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>M</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>9</v>
+      </c>
+      <c r="AK3">
+        <v>8</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>1</v>
+      </c>
+      <c r="AN3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>30903</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Đào Chí Dũng</v>
+      </c>
+      <c r="D4" t="str">
+        <v>E</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>E</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>M</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>E</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>M</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>M</v>
+      </c>
+      <c r="P4" t="str">
+        <v>E</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>E</v>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v>M</v>
+      </c>
+      <c r="T4" t="str">
+        <v>M</v>
+      </c>
+      <c r="U4" t="str">
+        <v>E</v>
+      </c>
+      <c r="V4" t="str">
+        <v>E</v>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v>M</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>E</v>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v>M</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>E</v>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v>M</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>M</v>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>9</v>
+      </c>
+      <c r="AK4">
+        <v>9</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>31930</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Phạm Ninh Toàn</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>M</v>
+      </c>
+      <c r="F5" t="str">
+        <v>M</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>E</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>M</v>
+      </c>
+      <c r="L5" t="str">
+        <v>E</v>
+      </c>
+      <c r="M5" t="str">
+        <v>E</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>E</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>M</v>
+      </c>
+      <c r="S5" t="str">
+        <v>M</v>
+      </c>
+      <c r="T5" t="str">
+        <v>E</v>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v>M</v>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v>E</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>E</v>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v>E</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>E</v>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v>M</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>E</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>7</v>
+      </c>
+      <c r="AK5">
+        <v>10</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>30322</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Nguyễn Thái Uy</v>
+      </c>
+      <c r="D6" t="str">
+        <v>M</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>E</v>
+      </c>
+      <c r="H6" t="str">
+        <v>E</v>
+      </c>
+      <c r="I6" t="str">
+        <v>E</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>M</v>
+      </c>
+      <c r="L6" t="str">
+        <v>M</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>M</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v>E</v>
+      </c>
+      <c r="T6" t="str">
+        <v>E</v>
+      </c>
+      <c r="U6" t="str">
+        <v>E</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v>M</v>
+      </c>
+      <c r="X6" t="str">
+        <v>M</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>E</v>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v>M</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>M</v>
+      </c>
+      <c r="AC6" t="str">
+        <v/>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <v/>
+      </c>
+      <c r="AF6" t="str">
+        <v>E</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>E</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>E</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>8</v>
+      </c>
+      <c r="AK6">
+        <v>10</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Công kế hoạch</v>
-      </c>
-      <c r="B7">
-        <v>25</v>
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>31845</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Nguyễn Ngọc Long</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>E</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>M</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>E</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>M</v>
+      </c>
+      <c r="M7" t="str">
+        <v>E</v>
+      </c>
+      <c r="N7" t="str">
+        <v>E</v>
+      </c>
+      <c r="O7" t="str">
+        <v>E</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v>M</v>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>M</v>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v>M</v>
+      </c>
+      <c r="X7" t="str">
+        <v>E</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>M</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>E</v>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v>M</v>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v>M</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>E</v>
+      </c>
+      <c r="AG7" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>8</v>
+      </c>
+      <c r="AK7">
+        <v>8</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Tháng 11/2026</v>
-      </c>
-      <c r="B8">
-        <v>200</v>
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>42014</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Nguyễn Xuân Tuyền</v>
+      </c>
+      <c r="D8" t="str">
+        <v>M</v>
+      </c>
+      <c r="E8" t="str">
+        <v>M</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>M</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>M</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>E</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>E</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>M</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>M</v>
+      </c>
+      <c r="R8" t="str">
+        <v>E</v>
+      </c>
+      <c r="S8" t="str">
+        <v>E</v>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v>M</v>
+      </c>
+      <c r="V8" t="str">
+        <v>M</v>
+      </c>
+      <c r="W8" t="str">
+        <v>E</v>
+      </c>
+      <c r="X8" t="str">
+        <v>E</v>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v>M</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>E</v>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v>M</v>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>10</v>
+      </c>
+      <c r="AK8">
+        <v>7</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DSP HDQ</v>
+      </c>
+      <c r="B9" t="str">
+        <v>30904</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Trần Đình Đạt</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>M</v>
+      </c>
+      <c r="H9" t="str">
+        <v>E</v>
+      </c>
+      <c r="I9" t="str">
+        <v>E</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>M</v>
+      </c>
+      <c r="L9" t="str">
+        <v>M</v>
+      </c>
+      <c r="M9" t="str">
+        <v>M</v>
+      </c>
+      <c r="N9" t="str">
+        <v>E</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>E</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>E</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v>M</v>
+      </c>
+      <c r="T9" t="str">
+        <v>E</v>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v>M</v>
+      </c>
+      <c r="X9" t="str">
+        <v>M</v>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v>M</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>E</v>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v>E</v>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v>M</v>
+      </c>
+      <c r="AG9" t="str">
+        <v>E</v>
+      </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>9</v>
+      </c>
+      <c r="AK9">
+        <v>9</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Vị trí trực</v>
+        <v/>
       </c>
       <c r="B10" t="str">
-        <v>Mã nhân viên</v>
+        <v>30905</v>
       </c>
       <c r="C10" t="str">
-        <v>Họ tên</v>
+        <v>Nguyễn Trương Hoàng Hưng</v>
       </c>
       <c r="D10" t="str">
-        <v>26</v>
+        <v>E</v>
       </c>
       <c r="E10" t="str">
-        <v>27</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>28</v>
+        <v>M</v>
       </c>
       <c r="G10" t="str">
-        <v>29</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>30</v>
+        <v>E</v>
       </c>
       <c r="I10" t="str">
-        <v>31</v>
+        <v/>
       </c>
       <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>E</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>M</v>
+      </c>
+      <c r="O10" t="str">
+        <v>E</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>M</v>
+      </c>
+      <c r="R10" t="str">
+        <v>E</v>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v>M</v>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v>M</v>
+      </c>
+      <c r="W10" t="str">
+        <v>P</v>
+      </c>
+      <c r="X10" t="str">
+        <v>P</v>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v>E</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>E</v>
+      </c>
+      <c r="AC10" t="str">
+        <v/>
+      </c>
+      <c r="AD10" t="str">
+        <v>M</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>M</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>E</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>NL</v>
+      </c>
+      <c r="AH10" t="str">
+        <v>SN</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>7</v>
+      </c>
+      <c r="AK10">
+        <v>8</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
         <v>1</v>
       </c>
-      <c r="K10" t="str">
-        <v>2</v>
-      </c>
-      <c r="L10" t="str">
-        <v>3</v>
-      </c>
-      <c r="M10" t="str">
-        <v>4</v>
-      </c>
-      <c r="N10" t="str">
-        <v>5</v>
-      </c>
-      <c r="O10" t="str">
-        <v>6</v>
-      </c>
-      <c r="P10" t="str">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>8</v>
-      </c>
-      <c r="R10" t="str">
-        <v>9</v>
-      </c>
-      <c r="S10" t="str">
-        <v>10</v>
-      </c>
-      <c r="T10" t="str">
-        <v>11</v>
-      </c>
-      <c r="U10" t="str">
-        <v>12</v>
-      </c>
-      <c r="V10" t="str">
-        <v>13</v>
-      </c>
-      <c r="W10" t="str">
-        <v>14</v>
-      </c>
-      <c r="X10" t="str">
-        <v>15</v>
-      </c>
-      <c r="Y10" t="str">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="str">
-        <v>17</v>
-      </c>
-      <c r="AA10" t="str">
-        <v>18</v>
-      </c>
-      <c r="AB10" t="str">
-        <v>19</v>
-      </c>
-      <c r="AC10" t="str">
-        <v>20</v>
-      </c>
-      <c r="AD10" t="str">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="str">
-        <v>22</v>
-      </c>
-      <c r="AF10" t="str">
-        <v>23</v>
-      </c>
-      <c r="AG10" t="str">
-        <v>24</v>
-      </c>
-      <c r="AH10" t="str">
-        <v>25</v>
-      </c>
-      <c r="AI10" t="str">
-        <v>Ca HC</v>
-      </c>
-      <c r="AJ10" t="str">
-        <v>Ca M</v>
-      </c>
-      <c r="AK10" t="str">
-        <v>Ca E</v>
-      </c>
-      <c r="AL10" t="str">
-        <v>Ca 9h-21h</v>
-      </c>
-      <c r="AM10" t="str">
-        <v>NL</v>
-      </c>
-      <c r="AN10" t="str">
-        <v>Tổng giờ công</v>
+      <c r="AN10">
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -550,162 +1669,162 @@
         <v/>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>30841</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>Vũ Hoàng Long</v>
       </c>
       <c r="D11" t="str">
-        <v>T2</v>
+        <v>M</v>
       </c>
       <c r="E11" t="str">
-        <v>T3</v>
+        <v>E</v>
       </c>
       <c r="F11" t="str">
-        <v>T4</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>T5</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>T6</v>
+        <v>M</v>
       </c>
       <c r="I11" t="str">
-        <v>T7</v>
+        <v>M</v>
       </c>
       <c r="J11" t="str">
-        <v>CN</v>
+        <v>M</v>
       </c>
       <c r="K11" t="str">
-        <v>T2</v>
+        <v/>
       </c>
       <c r="L11" t="str">
-        <v>T3</v>
+        <v>E</v>
       </c>
       <c r="M11" t="str">
-        <v>T4</v>
+        <v>E</v>
       </c>
       <c r="N11" t="str">
-        <v>T5</v>
+        <v/>
       </c>
       <c r="O11" t="str">
-        <v>T6</v>
+        <v/>
       </c>
       <c r="P11" t="str">
-        <v>T7</v>
+        <v>M</v>
       </c>
       <c r="Q11" t="str">
-        <v>CN</v>
+        <v/>
       </c>
       <c r="R11" t="str">
-        <v>T2</v>
+        <v/>
       </c>
       <c r="S11" t="str">
-        <v>T3</v>
+        <v/>
       </c>
       <c r="T11" t="str">
-        <v>T4</v>
+        <v>P</v>
       </c>
       <c r="U11" t="str">
-        <v>T5</v>
+        <v>E</v>
       </c>
       <c r="V11" t="str">
-        <v>T6</v>
+        <v/>
       </c>
       <c r="W11" t="str">
-        <v>T7</v>
+        <v>E</v>
       </c>
       <c r="X11" t="str">
-        <v>CN</v>
+        <v>E</v>
       </c>
       <c r="Y11" t="str">
-        <v>T2</v>
+        <v>E</v>
       </c>
       <c r="Z11" t="str">
-        <v>T3</v>
+        <v/>
       </c>
       <c r="AA11" t="str">
-        <v>T4</v>
+        <v>M</v>
       </c>
       <c r="AB11" t="str">
-        <v>T5</v>
+        <v>M</v>
       </c>
       <c r="AC11" t="str">
-        <v>T6</v>
+        <v>M</v>
       </c>
       <c r="AD11" t="str">
-        <v>T7</v>
+        <v/>
       </c>
       <c r="AE11" t="str">
-        <v>CN</v>
+        <v/>
       </c>
       <c r="AF11" t="str">
-        <v>T2</v>
+        <v>P</v>
       </c>
       <c r="AG11" t="str">
-        <v>T3</v>
+        <v>NL</v>
       </c>
       <c r="AH11" t="str">
-        <v>T4</v>
-      </c>
-      <c r="AI11" t="str">
-        <v/>
-      </c>
-      <c r="AJ11" t="str">
-        <v/>
-      </c>
-      <c r="AK11" t="str">
-        <v/>
-      </c>
-      <c r="AL11" t="str">
-        <v/>
-      </c>
-      <c r="AM11" t="str">
-        <v/>
-      </c>
-      <c r="AN11" t="str">
-        <v/>
+        <v>M</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>9</v>
+      </c>
+      <c r="AK11">
+        <v>7</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <v>216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Duty Manager</v>
+        <v/>
       </c>
       <c r="B12" t="str">
-        <v>30346</v>
+        <v>29718</v>
       </c>
       <c r="C12" t="str">
-        <v>Đàm Xuân Hiến</v>
+        <v>Vũ Huy Hùng</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="G12" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="H12" t="str">
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="K12" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="M12" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -714,16 +1833,16 @@
         <v>M</v>
       </c>
       <c r="P12" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="Q12" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="R12" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="S12" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -735,7 +1854,7 @@
         <v>E</v>
       </c>
       <c r="W12" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="X12" t="str">
         <v/>
@@ -744,19 +1863,19 @@
         <v>M</v>
       </c>
       <c r="Z12" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AA12" t="str">
         <v/>
       </c>
       <c r="AB12" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AC12" t="str">
         <v/>
       </c>
       <c r="AD12" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AE12" t="str">
         <v>E</v>
@@ -765,42 +1884,42 @@
         <v/>
       </c>
       <c r="AG12" t="str">
-        <v>NL</v>
+        <v>M</v>
       </c>
       <c r="AH12" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AI12">
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>DSP ASST HDQ</v>
       </c>
       <c r="B13" t="str">
-        <v>30903</v>
+        <v>39278</v>
       </c>
       <c r="C13" t="str">
-        <v>Đào Chí Dũng</v>
+        <v>Nguyền Kiều Huyền Chi</v>
       </c>
       <c r="D13" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -818,7 +1937,7 @@
         <v>M</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="K13" t="str">
         <v>E</v>
@@ -830,28 +1949,28 @@
         <v>M</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="O13" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="P13" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="R13" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="S13" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="T13" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="U13" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="V13" t="str">
         <v>E</v>
@@ -887,7 +2006,7 @@
         <v>M</v>
       </c>
       <c r="AG13" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AH13" t="str">
         <v/>
@@ -896,10 +2015,10 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -916,10 +2035,10 @@
         <v/>
       </c>
       <c r="B14" t="str">
-        <v>31930</v>
+        <v>39280</v>
       </c>
       <c r="C14" t="str">
-        <v>Phạm Ninh Toàn</v>
+        <v>Đặng Thảo Linh</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -931,97 +2050,97 @@
         <v>M</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="I14" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="K14" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="M14" t="str">
         <v>E</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="O14" t="str">
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="R14" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="S14" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="T14" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="U14" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="V14" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="W14" t="str">
         <v/>
       </c>
       <c r="X14" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="Y14" t="str">
         <v>E</v>
       </c>
       <c r="Z14" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AA14" t="str">
         <v/>
       </c>
       <c r="AB14" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AC14" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AD14" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AE14" t="str">
         <v/>
       </c>
       <c r="AF14" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AG14" t="str">
         <v>NL</v>
       </c>
       <c r="AH14" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AI14">
         <v>0</v>
       </c>
       <c r="AJ14">
+        <v>10</v>
+      </c>
+      <c r="AK14">
         <v>7</v>
-      </c>
-      <c r="AK14">
-        <v>10</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -1038,25 +2157,25 @@
         <v/>
       </c>
       <c r="B15" t="str">
-        <v>30322</v>
+        <v>39276</v>
       </c>
       <c r="C15" t="str">
-        <v>Nguyễn Thái Uy</v>
+        <v>Bùi Việt Anh</v>
       </c>
       <c r="D15" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="H15" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="I15" t="str">
         <v>E</v>
@@ -1068,7 +2187,7 @@
         <v>M</v>
       </c>
       <c r="L15" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1077,7 +2196,7 @@
         <v>M</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="P15" t="str">
         <v/>
@@ -1086,64 +2205,64 @@
         <v/>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="S15" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="T15" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="U15" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="V15" t="str">
         <v/>
       </c>
       <c r="W15" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="X15" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="Y15" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Z15" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AA15" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AB15" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AC15" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD15" t="str">
         <v/>
       </c>
       <c r="AE15" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AF15" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AG15" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AH15" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AI15">
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -1160,61 +2279,61 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>31845</v>
+        <v>39274</v>
       </c>
       <c r="C16" t="str">
-        <v>Nguyễn Ngọc Long</v>
+        <v>Đỗ Nam Anh</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="L16" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>E</v>
       </c>
       <c r="N16" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="O16" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="R16" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="S16" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="T16" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="U16" t="str">
         <v/>
@@ -1226,55 +2345,55 @@
         <v>M</v>
       </c>
       <c r="X16" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="Y16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="Z16" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AA16" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AB16" t="str">
         <v/>
       </c>
       <c r="AC16" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AD16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AE16" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AF16" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AG16" t="str">
-        <v>NL</v>
+        <v>M</v>
       </c>
       <c r="AH16" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AI16">
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK16">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17">
@@ -1282,19 +2401,19 @@
         <v/>
       </c>
       <c r="B17" t="str">
-        <v>42014</v>
+        <v>39272</v>
       </c>
       <c r="C17" t="str">
-        <v>Nguyễn Xuân Tuyền</v>
+        <v>Hoa Hữu Nghĩa</v>
       </c>
       <c r="D17" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="E17" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1303,34 +2422,34 @@
         <v>M</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="J17" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="P17" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Q17" t="str">
         <v>M</v>
       </c>
       <c r="R17" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="S17" t="str">
         <v>E</v>
@@ -1339,7 +2458,7 @@
         <v/>
       </c>
       <c r="U17" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="V17" t="str">
         <v>M</v>
@@ -1354,13 +2473,13 @@
         <v/>
       </c>
       <c r="Z17" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AA17" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AB17" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AC17" t="str">
         <v/>
@@ -1369,13 +2488,13 @@
         <v>M</v>
       </c>
       <c r="AE17" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AF17" t="str">
         <v/>
       </c>
       <c r="AG17" t="str">
-        <v>NL</v>
+        <v>E</v>
       </c>
       <c r="AH17" t="str">
         <v/>
@@ -1384,57 +2503,57 @@
         <v>0</v>
       </c>
       <c r="AJ17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>DSP HDQ</v>
+        <v>DSP SGN</v>
       </c>
       <c r="B18" t="str">
-        <v>30904</v>
+        <v>31844</v>
       </c>
       <c r="C18" t="str">
-        <v>Trần Đình Đạt</v>
+        <v>Nguyễn Hoàng Huy</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>HC</v>
       </c>
       <c r="G18" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="H18" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="K18" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="L18" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>M</v>
@@ -1446,7 +2565,7 @@
         <v/>
       </c>
       <c r="P18" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="Q18" t="str">
         <v>E</v>
@@ -1464,10 +2583,10 @@
         <v/>
       </c>
       <c r="V18" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="W18" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="X18" t="str">
         <v>M</v>
@@ -1476,7 +2595,7 @@
         <v/>
       </c>
       <c r="Z18" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AA18" t="str">
         <v>E</v>
@@ -1485,28 +2604,28 @@
         <v/>
       </c>
       <c r="AC18" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AD18" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AE18" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AF18" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AG18" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AH18" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK18">
         <v>9</v>
@@ -1518,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="AN18">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19">
@@ -1526,91 +2645,91 @@
         <v/>
       </c>
       <c r="B19" t="str">
-        <v>30905</v>
+        <v>31843</v>
       </c>
       <c r="C19" t="str">
-        <v>Nguyễn Trương Hoàng Hưng</v>
+        <v>Lương Trung Hiếu</v>
       </c>
       <c r="D19" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="F19" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="H19" t="str">
         <v>E</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="O19" t="str">
-        <v>E</v>
+        <v>SN</v>
       </c>
       <c r="P19" t="str">
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="R19" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="S19" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="T19" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="U19" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="V19" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="W19" t="str">
-        <v>P</v>
+        <v/>
       </c>
       <c r="X19" t="str">
-        <v>P</v>
+        <v>E</v>
       </c>
       <c r="Y19" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="Z19" t="str">
         <v/>
       </c>
       <c r="AA19" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AB19" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AC19" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AD19" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AE19" t="str">
         <v>M</v>
@@ -1622,13 +2741,13 @@
         <v>NL</v>
       </c>
       <c r="AH19" t="str">
-        <v>SN</v>
+        <v/>
       </c>
       <c r="AI19">
         <v>0</v>
       </c>
       <c r="AJ19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK19">
         <v>8</v>
@@ -1640,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="AN19">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
@@ -1648,19 +2767,19 @@
         <v/>
       </c>
       <c r="B20" t="str">
-        <v>30841</v>
+        <v>31846</v>
       </c>
       <c r="C20" t="str">
-        <v>Vũ Hoàng Long</v>
+        <v>Nguyễn Phúc Thịnh</v>
       </c>
       <c r="D20" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1672,97 +2791,97 @@
         <v>M</v>
       </c>
       <c r="J20" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="M20" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="P20" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="T20" t="str">
-        <v>P</v>
+        <v/>
       </c>
       <c r="U20" t="str">
-        <v>E</v>
+        <v>HC</v>
       </c>
       <c r="V20" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="W20" t="str">
         <v>E</v>
       </c>
       <c r="X20" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Y20" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="Z20" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AA20" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AB20" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AC20" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AD20" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AE20" t="str">
         <v/>
       </c>
       <c r="AF20" t="str">
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="AG20" t="str">
-        <v>NL</v>
+        <v>E</v>
       </c>
       <c r="AH20" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20">
+        <v>8</v>
+      </c>
+      <c r="AK20">
         <v>9</v>
       </c>
-      <c r="AK20">
-        <v>7</v>
-      </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
@@ -1770,40 +2889,40 @@
         <v/>
       </c>
       <c r="B21" t="str">
-        <v>29718</v>
+        <v>31847</v>
       </c>
       <c r="C21" t="str">
-        <v>Vũ Huy Hùng</v>
+        <v>Hoàng Bảo Ngọc</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="E21" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="G21" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>SN</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1818,28 +2937,28 @@
         <v/>
       </c>
       <c r="R21" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="S21" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="T21" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="U21" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="V21" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="W21" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="X21" t="str">
         <v/>
       </c>
       <c r="Y21" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Z21" t="str">
         <v>E</v>
@@ -1851,10 +2970,10 @@
         <v>M</v>
       </c>
       <c r="AC21" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD21" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AE21" t="str">
         <v>E</v>
@@ -1863,7 +2982,7 @@
         <v/>
       </c>
       <c r="AG21" t="str">
-        <v>M</v>
+        <v>NL</v>
       </c>
       <c r="AH21" t="str">
         <v>E</v>
@@ -1875,72 +2994,72 @@
         <v>7</v>
       </c>
       <c r="AK21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DSP ASST HDQ</v>
+        <v/>
       </c>
       <c r="B22" t="str">
-        <v>39278</v>
+        <v>43311</v>
       </c>
       <c r="C22" t="str">
-        <v>Nguyền Kiều Huyền Chi</v>
+        <v>Đinh Minh Trí</v>
       </c>
       <c r="D22" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="G22" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="I22" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="J22" t="str">
         <v>E</v>
       </c>
       <c r="K22" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="M22" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="N22" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="O22" t="str">
-        <v>E</v>
+        <v>HC</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="Q22" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="R22" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="S22" t="str">
         <v>E</v>
@@ -1952,61 +3071,61 @@
         <v/>
       </c>
       <c r="V22" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="W22" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="X22" t="str">
         <v/>
       </c>
       <c r="Y22" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Z22" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AA22" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AB22" t="str">
         <v/>
       </c>
       <c r="AC22" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AD22" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AE22" t="str">
         <v/>
       </c>
       <c r="AF22" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AG22" t="str">
-        <v>E</v>
+        <v>NL</v>
       </c>
       <c r="AH22" t="str">
         <v/>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23">
@@ -2014,22 +3133,22 @@
         <v/>
       </c>
       <c r="B23" t="str">
-        <v>39280</v>
+        <v>43315</v>
       </c>
       <c r="C23" t="str">
-        <v>Đặng Thảo Linh</v>
+        <v>Huỳnh Tấn Phước</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="E23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>E</v>
@@ -2041,58 +3160,58 @@
         <v>M</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="L23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="M23" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="N23" t="str">
         <v>E</v>
       </c>
       <c r="O23" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="P23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="R23" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="S23" t="str">
         <v/>
       </c>
       <c r="T23" t="str">
-        <v>M</v>
+        <v>HC</v>
       </c>
       <c r="U23" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="V23" t="str">
         <v/>
       </c>
       <c r="W23" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="X23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Y23" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="Z23" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AA23" t="str">
         <v/>
       </c>
       <c r="AB23" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AC23" t="str">
         <v/>
@@ -2101,31 +3220,31 @@
         <v/>
       </c>
       <c r="AE23" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AF23" t="str">
         <v>E</v>
       </c>
       <c r="AG23" t="str">
-        <v>NL</v>
+        <v>E</v>
       </c>
       <c r="AH23" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN23">
         <v>212</v>
@@ -2136,19 +3255,19 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v>39276</v>
+        <v>43337</v>
       </c>
       <c r="C24" t="str">
-        <v>Bùi Việt Anh</v>
+        <v>Vũ Trọng Khánh</v>
       </c>
       <c r="D24" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="E24" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="G24" t="str">
         <v>M</v>
@@ -2157,13 +3276,13 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>E</v>
+        <v>HC</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="L24" t="str">
         <v>E</v>
@@ -2172,31 +3291,31 @@
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="O24" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="Q24" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="R24" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="S24" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="T24" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="U24" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="V24" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="W24" t="str">
         <v/>
@@ -2205,16 +3324,16 @@
         <v>E</v>
       </c>
       <c r="Y24" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="Z24" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AA24" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AB24" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AC24" t="str">
         <v>E</v>
@@ -2223,7 +3342,7 @@
         <v/>
       </c>
       <c r="AE24" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AF24" t="str">
         <v/>
@@ -2232,16 +3351,16 @@
         <v>M</v>
       </c>
       <c r="AH24" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -2250,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="AN24">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25">
@@ -2258,37 +3377,37 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>39274</v>
+        <v>43313</v>
       </c>
       <c r="C25" t="str">
-        <v>Đỗ Nam Anh</v>
+        <v>Cù Trường Phú</v>
       </c>
       <c r="D25" t="str">
         <v>E</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="F25" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="H25" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="J25" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="M25" t="str">
         <v>E</v>
@@ -2297,49 +3416,49 @@
         <v/>
       </c>
       <c r="O25" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="P25" t="str">
-        <v>E</v>
+        <v>HC</v>
       </c>
       <c r="Q25" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="T25" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="U25" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="V25" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="W25" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="X25" t="str">
         <v>M</v>
       </c>
       <c r="Y25" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Z25" t="str">
         <v/>
       </c>
       <c r="AA25" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AB25" t="str">
         <v/>
       </c>
       <c r="AC25" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AD25" t="str">
         <v>E</v>
@@ -2348,75 +3467,75 @@
         <v/>
       </c>
       <c r="AF25" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AG25" t="str">
-        <v>M</v>
+        <v>NL</v>
       </c>
       <c r="AH25" t="str">
-        <v>E</v>
+        <v>M</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN25">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>DSP PQC</v>
       </c>
       <c r="B26" t="str">
-        <v>39272</v>
+        <v>41863</v>
       </c>
       <c r="C26" t="str">
-        <v>Hoa Hữu Nghĩa</v>
+        <v>Lê Ngọc Thành Tài</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="F26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="H26" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="J26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="O26" t="str">
         <v>E</v>
@@ -2425,99 +3544,99 @@
         <v/>
       </c>
       <c r="Q26" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="R26" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="S26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="T26" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="U26" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="V26" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="W26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="X26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Y26" t="str">
         <v/>
       </c>
       <c r="Z26" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AA26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AB26" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="AC26" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD26" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AE26" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="AF26" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AG26" t="str">
-        <v>E</v>
+        <v>NL</v>
       </c>
       <c r="AH26" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="AI26">
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AK26">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN26">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>DSP SGN</v>
+        <v/>
       </c>
       <c r="B27" t="str">
-        <v>31844</v>
+        <v>41865</v>
       </c>
       <c r="C27" t="str">
-        <v>Nguyễn Hoàng Huy</v>
+        <v>Nguyễn Đức Lộc</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="E27" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="F27" t="str">
-        <v>HC</v>
+        <v>E</v>
       </c>
       <c r="G27" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -2526,7 +3645,7 @@
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="K27" t="str">
         <v>E</v>
@@ -2535,58 +3654,58 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="N27" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="O27" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="P27" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="Q27" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="R27" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="S27" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="T27" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="U27" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="V27" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="W27" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="X27" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="Y27" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="Z27" t="str">
         <v/>
       </c>
       <c r="AA27" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="AB27" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AC27" t="str">
         <v/>
       </c>
       <c r="AD27" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="AE27" t="str">
         <v>E</v>
@@ -2595,28 +3714,28 @@
         <v/>
       </c>
       <c r="AG27" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="AH27" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AI27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
         <v>8</v>
       </c>
-      <c r="AK27">
-        <v>9</v>
-      </c>
       <c r="AL27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM27">
         <v>0</v>
       </c>
       <c r="AN27">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28">
@@ -2624,150 +3743,150 @@
         <v/>
       </c>
       <c r="B28" t="str">
-        <v>31843</v>
+        <v>41867</v>
       </c>
       <c r="C28" t="str">
-        <v>Lương Trung Hiếu</v>
+        <v>Phan Thành Nghĩa</v>
       </c>
       <c r="D28" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="E28" t="str">
-        <v>E</v>
+        <v>HC</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="G28" t="str">
-        <v>M</v>
+        <v>HC</v>
       </c>
       <c r="H28" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="I28" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="K28" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="L28" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>SN</v>
       </c>
       <c r="O28" t="str">
-        <v>SN</v>
+        <v/>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="Q28" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="R28" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="S28" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="T28" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="U28" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="V28" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="W28" t="str">
         <v/>
       </c>
       <c r="X28" t="str">
-        <v>E</v>
+        <v>C9</v>
       </c>
       <c r="Y28" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Z28" t="str">
-        <v/>
+        <v>C9</v>
       </c>
       <c r="AA28" t="str">
-        <v>M</v>
+        <v>E</v>
       </c>
       <c r="AB28" t="str">
         <v/>
       </c>
       <c r="AC28" t="str">
-        <v>M</v>
+        <v>C9</v>
       </c>
       <c r="AD28" t="str">
-        <v/>
+        <v>E</v>
       </c>
       <c r="AE28" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AF28" t="str">
         <v>E</v>
       </c>
       <c r="AG28" t="str">
-        <v>NL</v>
+        <v>E</v>
       </c>
       <c r="AH28" t="str">
         <v/>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AM28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>BRF SGN</v>
       </c>
       <c r="B29" t="str">
-        <v>31846</v>
+        <v>32117</v>
       </c>
       <c r="C29" t="str">
-        <v>Nguyễn Phúc Thịnh</v>
+        <v>Lê Song Huyền Vi</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="F29" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="H29" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="I29" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -2779,79 +3898,79 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="N29" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="O29" t="str">
-        <v>E</v>
+        <v>NC</v>
       </c>
       <c r="P29" t="str">
         <v/>
       </c>
       <c r="Q29" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="R29" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="S29" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="T29" t="str">
         <v/>
       </c>
       <c r="U29" t="str">
+        <v>PT</v>
+      </c>
+      <c r="V29" t="str">
+        <v>PT</v>
+      </c>
+      <c r="W29" t="str">
+        <v>PT</v>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
+        <v>PS</v>
+      </c>
+      <c r="Z29" t="str">
+        <v/>
+      </c>
+      <c r="AA29" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AB29" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AC29" t="str">
+        <v/>
+      </c>
+      <c r="AD29" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AE29" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>ST</v>
+      </c>
+      <c r="AG29" t="str">
         <v>HC</v>
       </c>
-      <c r="V29" t="str">
-        <v>M</v>
-      </c>
-      <c r="W29" t="str">
-        <v>E</v>
-      </c>
-      <c r="X29" t="str">
-        <v/>
-      </c>
-      <c r="Y29" t="str">
-        <v>M</v>
-      </c>
-      <c r="Z29" t="str">
-        <v>M</v>
-      </c>
-      <c r="AA29" t="str">
-        <v/>
-      </c>
-      <c r="AB29" t="str">
-        <v>E</v>
-      </c>
-      <c r="AC29" t="str">
-        <v>E</v>
-      </c>
-      <c r="AD29" t="str">
-        <v>E</v>
-      </c>
-      <c r="AE29" t="str">
-        <v/>
-      </c>
-      <c r="AF29" t="str">
-        <v>M</v>
-      </c>
-      <c r="AG29" t="str">
-        <v>E</v>
-      </c>
       <c r="AH29" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="AI29">
         <v>1</v>
       </c>
       <c r="AJ29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -2860,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="AN29">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
@@ -2868,70 +3987,70 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>31847</v>
+        <v>32115</v>
       </c>
       <c r="C30" t="str">
-        <v>Hoàng Bảo Ngọc</v>
+        <v>Đoàn Văn Tây</v>
       </c>
       <c r="D30" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="F30" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="H30" t="str">
-        <v>SN</v>
+        <v>SS</v>
       </c>
       <c r="I30" t="str">
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="K30" t="str">
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="M30" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="O30" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="P30" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="Q30" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="R30" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="S30" t="str">
         <v/>
       </c>
       <c r="T30" t="str">
-        <v>M</v>
+        <v>SS</v>
       </c>
       <c r="U30" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="V30" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="W30" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="X30" t="str">
         <v/>
@@ -2940,49 +4059,49 @@
         <v/>
       </c>
       <c r="Z30" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AA30" t="str">
         <v/>
       </c>
       <c r="AB30" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AC30" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="AD30" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="AE30" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AF30" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="AG30" t="str">
-        <v>NL</v>
+        <v>SS</v>
       </c>
       <c r="AH30" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="AI30">
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31">
@@ -2990,82 +4109,82 @@
         <v/>
       </c>
       <c r="B31" t="str">
-        <v>43311</v>
+        <v>31969</v>
       </c>
       <c r="C31" t="str">
-        <v>Đinh Minh Trí</v>
+        <v>Nguyễn Thị Mỹ Hương</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="E31" t="str">
-        <v>M</v>
+        <v>SS</v>
       </c>
       <c r="F31" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="J31" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="L31" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>M</v>
+        <v>SS</v>
       </c>
       <c r="O31" t="str">
-        <v>HC</v>
+        <v>SS</v>
       </c>
       <c r="P31" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
         <v/>
       </c>
       <c r="R31" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="S31" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="T31" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="U31" t="str">
         <v/>
       </c>
       <c r="V31" t="str">
-        <v>M</v>
+        <v>SS</v>
       </c>
       <c r="W31" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="X31" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="Y31" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="Z31" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="AA31" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AB31" t="str">
         <v/>
@@ -3074,37 +4193,37 @@
         <v/>
       </c>
       <c r="AD31" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AE31" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="AF31" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AG31" t="str">
-        <v>NL</v>
+        <v>ST</v>
       </c>
       <c r="AH31" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="AI31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32">
@@ -3112,112 +4231,112 @@
         <v/>
       </c>
       <c r="B32" t="str">
-        <v>43315</v>
+        <v>37388</v>
       </c>
       <c r="C32" t="str">
-        <v>Huỳnh Tấn Phước</v>
+        <v>Trương Thị Ngọc Loan</v>
       </c>
       <c r="D32" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="J32" t="str">
-        <v>M</v>
+        <v>SS</v>
       </c>
       <c r="K32" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="M32" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="O32" t="str">
-        <v>E</v>
+        <v>ST</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>ST</v>
       </c>
       <c r="Q32" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="R32" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="S32" t="str">
         <v/>
       </c>
       <c r="T32" t="str">
-        <v>HC</v>
+        <v/>
       </c>
       <c r="U32" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="V32" t="str">
         <v/>
       </c>
       <c r="W32" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="X32" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="Y32" t="str">
-        <v>M</v>
+        <v>SS</v>
       </c>
       <c r="Z32" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="AA32" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="AB32" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="AC32" t="str">
-        <v/>
+        <v>SS</v>
       </c>
       <c r="AD32" t="str">
         <v/>
       </c>
       <c r="AE32" t="str">
-        <v>M</v>
+        <v>ST</v>
       </c>
       <c r="AF32" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AG32" t="str">
-        <v>E</v>
+        <v>SS</v>
       </c>
       <c r="AH32" t="str">
         <v/>
       </c>
       <c r="AI32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -3226,120 +4345,120 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>BRF PQC</v>
       </c>
       <c r="B33" t="str">
-        <v>43337</v>
+        <v>41366</v>
       </c>
       <c r="C33" t="str">
-        <v>Vũ Trọng Khánh</v>
+        <v>Phan Như Ngọc</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>PS1</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>PS1</v>
       </c>
       <c r="F33" t="str">
-        <v>M</v>
+        <v>PS1</v>
       </c>
       <c r="G33" t="str">
-        <v>M</v>
+        <v>PS1</v>
       </c>
       <c r="H33" t="str">
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>HC</v>
+        <v/>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>PT</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="L33" t="str">
-        <v>E</v>
+        <v>PT1</v>
       </c>
       <c r="M33" t="str">
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="O33" t="str">
         <v/>
       </c>
       <c r="P33" t="str">
-        <v>M</v>
+        <v>PT1</v>
       </c>
       <c r="Q33" t="str">
-        <v>E</v>
+        <v>PT1</v>
       </c>
       <c r="R33" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="S33" t="str">
-        <v>M</v>
+        <v>PT1</v>
       </c>
       <c r="T33" t="str">
-        <v>E</v>
+        <v>PT1</v>
       </c>
       <c r="U33" t="str">
         <v/>
       </c>
       <c r="V33" t="str">
-        <v>E</v>
+        <v>PS</v>
       </c>
       <c r="W33" t="str">
         <v/>
       </c>
       <c r="X33" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Y33" t="str">
-        <v>E</v>
+        <v>PT</v>
       </c>
       <c r="Z33" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="AA33" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AB33" t="str">
-        <v>M</v>
+        <v>PS</v>
       </c>
       <c r="AC33" t="str">
-        <v>E</v>
+        <v>PT</v>
       </c>
       <c r="AD33" t="str">
-        <v/>
+        <v>PT</v>
       </c>
       <c r="AE33" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AF33" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="AG33" t="str">
-        <v>M</v>
+        <v>PS</v>
       </c>
       <c r="AH33" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AI33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -3348,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="AN33">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34">
@@ -3356,49 +4475,49 @@
         <v/>
       </c>
       <c r="B34" t="str">
-        <v>43313</v>
+        <v>41861</v>
       </c>
       <c r="C34" t="str">
-        <v>Cù Trường Phú</v>
+        <v>Phan Hiền Phúc Đạt</v>
       </c>
       <c r="D34" t="str">
-        <v>E</v>
+        <v>PS1</v>
       </c>
       <c r="E34" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>E</v>
+        <v>PT1</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="I34" t="str">
-        <v>M</v>
+        <v>PT1</v>
       </c>
       <c r="J34" t="str">
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="L34" t="str">
-        <v>E</v>
+        <v>PS</v>
       </c>
       <c r="M34" t="str">
-        <v>E</v>
+        <v>PS1</v>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="O34" t="str">
-        <v>M</v>
+        <v>PS</v>
       </c>
       <c r="P34" t="str">
-        <v>HC</v>
+        <v>PS1</v>
       </c>
       <c r="Q34" t="str">
         <v/>
@@ -3410,132 +4529,132 @@
         <v/>
       </c>
       <c r="T34" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="U34" t="str">
-        <v>E</v>
+        <v>PT</v>
       </c>
       <c r="V34" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="W34" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="X34" t="str">
-        <v>M</v>
+        <v>PS</v>
       </c>
       <c r="Y34" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="Z34" t="str">
         <v/>
       </c>
       <c r="AA34" t="str">
-        <v/>
+        <v>PT</v>
       </c>
       <c r="AB34" t="str">
-        <v/>
+        <v>PT</v>
       </c>
       <c r="AC34" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AD34" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AE34" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="AF34" t="str">
-        <v>M</v>
+        <v>PS</v>
       </c>
       <c r="AG34" t="str">
-        <v>NL</v>
+        <v>PT</v>
       </c>
       <c r="AH34" t="str">
-        <v>M</v>
+        <v>PT</v>
       </c>
       <c r="AI34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>DSP PQC</v>
+        <v/>
       </c>
       <c r="B35" t="str">
-        <v>41863</v>
+        <v>42791</v>
       </c>
       <c r="C35" t="str">
-        <v>Lê Ngọc Thành Tài</v>
+        <v>Nguyễn Phương Linh</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="E35" t="str">
-        <v>C9</v>
+        <v>PT1</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="G35" t="str">
-        <v>C9</v>
+        <v/>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>PS1</v>
       </c>
       <c r="I35" t="str">
-        <v>C9</v>
+        <v>PS1</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="K35" t="str">
-        <v>C9</v>
+        <v>PS1</v>
       </c>
       <c r="L35" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>PT1</v>
       </c>
       <c r="N35" t="str">
-        <v>C9</v>
+        <v>PT1</v>
       </c>
       <c r="O35" t="str">
-        <v>E</v>
+        <v>PT1</v>
       </c>
       <c r="P35" t="str">
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>C9</v>
+        <v>PS1</v>
       </c>
       <c r="R35" t="str">
-        <v>E</v>
+        <v>PS1</v>
       </c>
       <c r="S35" t="str">
-        <v/>
+        <v>PS1</v>
       </c>
       <c r="T35" t="str">
-        <v>C9</v>
+        <v>PS1</v>
       </c>
       <c r="U35" t="str">
-        <v>M</v>
+        <v>PS</v>
       </c>
       <c r="V35" t="str">
         <v/>
@@ -3544,1158 +4663,87 @@
         <v/>
       </c>
       <c r="X35" t="str">
-        <v/>
+        <v>PT</v>
       </c>
       <c r="Y35" t="str">
         <v/>
       </c>
       <c r="Z35" t="str">
-        <v>E</v>
+        <v>PS1</v>
       </c>
       <c r="AA35" t="str">
-        <v/>
+        <v>PS</v>
       </c>
       <c r="AB35" t="str">
-        <v>C9</v>
+        <v/>
       </c>
       <c r="AC35" t="str">
-        <v>E</v>
+        <v>PS1</v>
       </c>
       <c r="AD35" t="str">
         <v/>
       </c>
       <c r="AE35" t="str">
-        <v>C9</v>
+        <v/>
       </c>
       <c r="AF35" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="AG35" t="str">
-        <v>NL</v>
+        <v>HC</v>
       </c>
       <c r="AH35" t="str">
-        <v>C9</v>
+        <v>PS1</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v/>
-      </c>
-      <c r="B36" t="str">
-        <v>41865</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Nguyễn Đức Lộc</v>
-      </c>
-      <c r="D36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="E36" t="str">
-        <v>E</v>
-      </c>
-      <c r="F36" t="str">
-        <v>E</v>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
-      <c r="J36" t="str">
-        <v/>
-      </c>
-      <c r="K36" t="str">
-        <v>E</v>
-      </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="M36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="O36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="P36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="Q36" t="str">
-        <v/>
-      </c>
-      <c r="R36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="S36" t="str">
-        <v>E</v>
-      </c>
-      <c r="T36" t="str">
-        <v/>
-      </c>
-      <c r="U36" t="str">
-        <v>E</v>
-      </c>
-      <c r="V36" t="str">
-        <v/>
-      </c>
-      <c r="W36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="X36" t="str">
-        <v/>
-      </c>
-      <c r="Y36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="Z36" t="str">
-        <v/>
-      </c>
-      <c r="AA36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="AB36" t="str">
-        <v>E</v>
-      </c>
-      <c r="AC36" t="str">
-        <v/>
-      </c>
-      <c r="AD36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="AE36" t="str">
-        <v>E</v>
-      </c>
-      <c r="AF36" t="str">
-        <v/>
-      </c>
-      <c r="AG36" t="str">
-        <v>C9</v>
-      </c>
-      <c r="AH36" t="str">
-        <v>E</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
-      <c r="AJ36">
-        <v>0</v>
-      </c>
-      <c r="AK36">
-        <v>8</v>
-      </c>
-      <c r="AL36">
-        <v>10</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
         <v>216</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v/>
-      </c>
-      <c r="B37" t="str">
-        <v>41867</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Phan Thành Nghĩa</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v>HC</v>
-      </c>
-      <c r="F37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="G37" t="str">
-        <v>HC</v>
-      </c>
-      <c r="H37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-      <c r="J37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
-      <c r="N37" t="str">
-        <v>SN</v>
-      </c>
-      <c r="O37" t="str">
-        <v/>
-      </c>
-      <c r="P37" t="str">
-        <v>E</v>
-      </c>
-      <c r="Q37" t="str">
-        <v>E</v>
-      </c>
-      <c r="R37" t="str">
-        <v/>
-      </c>
-      <c r="S37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="T37" t="str">
-        <v>E</v>
-      </c>
-      <c r="U37" t="str">
-        <v/>
-      </c>
-      <c r="V37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="W37" t="str">
-        <v/>
-      </c>
-      <c r="X37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="Y37" t="str">
-        <v/>
-      </c>
-      <c r="Z37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="AA37" t="str">
-        <v>E</v>
-      </c>
-      <c r="AB37" t="str">
-        <v/>
-      </c>
-      <c r="AC37" t="str">
-        <v>C9</v>
-      </c>
-      <c r="AD37" t="str">
-        <v>E</v>
-      </c>
-      <c r="AE37" t="str">
-        <v/>
-      </c>
-      <c r="AF37" t="str">
-        <v>E</v>
-      </c>
-      <c r="AG37" t="str">
-        <v>E</v>
-      </c>
-      <c r="AH37" t="str">
-        <v/>
-      </c>
-      <c r="AI37">
-        <v>2</v>
-      </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
-      <c r="AK37">
-        <v>7</v>
-      </c>
-      <c r="AL37">
-        <v>9</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>BRF SGN</v>
-      </c>
-      <c r="B38" t="str">
-        <v>32117</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Lê Song Huyền Vi</v>
-      </c>
-      <c r="D38" t="str">
-        <v>SS</v>
-      </c>
-      <c r="E38" t="str">
-        <v>SS</v>
-      </c>
-      <c r="F38" t="str">
-        <v/>
-      </c>
-      <c r="G38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="H38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
-      <c r="J38" t="str">
-        <v/>
-      </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
-        <v/>
-      </c>
-      <c r="M38" t="str">
-        <v>SS</v>
-      </c>
-      <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="O38" t="str">
-        <v>NC</v>
-      </c>
-      <c r="P38" t="str">
-        <v/>
-      </c>
-      <c r="Q38" t="str">
-        <v/>
-      </c>
-      <c r="R38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="S38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="T38" t="str">
-        <v/>
-      </c>
-      <c r="U38" t="str">
-        <v>PT</v>
-      </c>
-      <c r="V38" t="str">
-        <v>PT</v>
-      </c>
-      <c r="W38" t="str">
-        <v>PT</v>
-      </c>
-      <c r="X38" t="str">
-        <v/>
-      </c>
-      <c r="Y38" t="str">
-        <v>PS</v>
-      </c>
-      <c r="Z38" t="str">
-        <v/>
-      </c>
-      <c r="AA38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AB38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AC38" t="str">
-        <v/>
-      </c>
-      <c r="AD38" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AE38" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AF38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AG38" t="str">
-        <v>HC</v>
-      </c>
-      <c r="AH38" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AI38">
-        <v>1</v>
-      </c>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
-      <c r="AK38">
-        <v>0</v>
-      </c>
-      <c r="AL38">
-        <v>0</v>
-      </c>
-      <c r="AM38">
-        <v>0</v>
-      </c>
-      <c r="AN38">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v/>
-      </c>
-      <c r="B39" t="str">
-        <v>32115</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Đoàn Văn Tây</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="H39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="J39" t="str">
-        <v/>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="M39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="N39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="O39" t="str">
-        <v/>
-      </c>
-      <c r="P39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="Q39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="R39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="S39" t="str">
-        <v/>
-      </c>
-      <c r="T39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="U39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="V39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="W39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="X39" t="str">
-        <v/>
-      </c>
-      <c r="Y39" t="str">
-        <v/>
-      </c>
-      <c r="Z39" t="str">
-        <v/>
-      </c>
-      <c r="AA39" t="str">
-        <v/>
-      </c>
-      <c r="AB39" t="str">
-        <v/>
-      </c>
-      <c r="AC39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AD39" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AE39" t="str">
-        <v/>
-      </c>
-      <c r="AF39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AG39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AH39" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AI39">
-        <v>0</v>
-      </c>
-      <c r="AJ39">
-        <v>0</v>
-      </c>
-      <c r="AK39">
-        <v>0</v>
-      </c>
-      <c r="AL39">
-        <v>0</v>
-      </c>
-      <c r="AM39">
-        <v>0</v>
-      </c>
-      <c r="AN39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v/>
-      </c>
-      <c r="B40" t="str">
-        <v>31969</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Nguyễn Thị Mỹ Hương</v>
-      </c>
-      <c r="D40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="E40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="F40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="J40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="K40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="O40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="P40" t="str">
-        <v/>
-      </c>
-      <c r="Q40" t="str">
-        <v/>
-      </c>
-      <c r="R40" t="str">
-        <v/>
-      </c>
-      <c r="S40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="T40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="U40" t="str">
-        <v/>
-      </c>
-      <c r="V40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="W40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="X40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="Y40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="Z40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AA40" t="str">
-        <v/>
-      </c>
-      <c r="AB40" t="str">
-        <v/>
-      </c>
-      <c r="AC40" t="str">
-        <v/>
-      </c>
-      <c r="AD40" t="str">
-        <v/>
-      </c>
-      <c r="AE40" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AF40" t="str">
-        <v/>
-      </c>
-      <c r="AG40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AH40" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AI40">
-        <v>0</v>
-      </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
-      <c r="AK40">
-        <v>0</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v/>
-      </c>
-      <c r="B41" t="str">
-        <v>37388</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Trương Thị Ngọc Loan</v>
-      </c>
-      <c r="D41" t="str">
-        <v>ST</v>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="J41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="K41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="L41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <v>ST</v>
-      </c>
-      <c r="P41" t="str">
-        <v>ST</v>
-      </c>
-      <c r="Q41" t="str">
-        <v>ST</v>
-      </c>
-      <c r="R41" t="str">
-        <v/>
-      </c>
-      <c r="S41" t="str">
-        <v/>
-      </c>
-      <c r="T41" t="str">
-        <v/>
-      </c>
-      <c r="U41" t="str">
-        <v>ST</v>
-      </c>
-      <c r="V41" t="str">
-        <v/>
-      </c>
-      <c r="W41" t="str">
-        <v/>
-      </c>
-      <c r="X41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="Y41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="Z41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AA41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AB41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AC41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AD41" t="str">
-        <v/>
-      </c>
-      <c r="AE41" t="str">
-        <v>ST</v>
-      </c>
-      <c r="AF41" t="str">
-        <v/>
-      </c>
-      <c r="AG41" t="str">
-        <v>SS</v>
-      </c>
-      <c r="AH41" t="str">
-        <v/>
-      </c>
-      <c r="AI41">
-        <v>0</v>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>0</v>
-      </c>
-      <c r="AN41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>BRF PQC</v>
-      </c>
-      <c r="B42" t="str">
-        <v>41366</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Phan Như Ngọc</v>
-      </c>
-      <c r="D42" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="E42" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="F42" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="G42" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="J42" t="str">
-        <v>PT</v>
-      </c>
-      <c r="K42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="L42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <v/>
-      </c>
-      <c r="P42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="Q42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="R42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="S42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="T42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="U42" t="str">
-        <v/>
-      </c>
-      <c r="V42" t="str">
-        <v>PS</v>
-      </c>
-      <c r="W42" t="str">
-        <v/>
-      </c>
-      <c r="X42" t="str">
-        <v/>
-      </c>
-      <c r="Y42" t="str">
-        <v>PT</v>
-      </c>
-      <c r="Z42" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="AA42" t="str">
-        <v/>
-      </c>
-      <c r="AB42" t="str">
-        <v>PS</v>
-      </c>
-      <c r="AC42" t="str">
-        <v>PT</v>
-      </c>
-      <c r="AD42" t="str">
-        <v>PT</v>
-      </c>
-      <c r="AE42" t="str">
-        <v/>
-      </c>
-      <c r="AF42" t="str">
-        <v>PS</v>
-      </c>
-      <c r="AG42" t="str">
-        <v>PS</v>
-      </c>
-      <c r="AH42" t="str">
-        <v/>
-      </c>
-      <c r="AI42">
-        <v>0</v>
-      </c>
-      <c r="AJ42">
-        <v>0</v>
-      </c>
-      <c r="AK42">
-        <v>0</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>0</v>
-      </c>
-      <c r="AN42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v/>
-      </c>
-      <c r="B43" t="str">
-        <v>41861</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Phan Hiền Phúc Đạt</v>
-      </c>
-      <c r="D43" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="H43" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="I43" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="J43" t="str">
-        <v/>
-      </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="M43" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="N43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="O43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="P43" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="Q43" t="str">
-        <v/>
-      </c>
-      <c r="R43" t="str">
-        <v/>
-      </c>
-      <c r="S43" t="str">
-        <v/>
-      </c>
-      <c r="T43" t="str">
-        <v/>
-      </c>
-      <c r="U43" t="str">
-        <v>PT</v>
-      </c>
-      <c r="V43" t="str">
-        <v/>
-      </c>
-      <c r="W43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="X43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="Y43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="Z43" t="str">
-        <v/>
-      </c>
-      <c r="AA43" t="str">
-        <v>PT</v>
-      </c>
-      <c r="AB43" t="str">
-        <v>PT</v>
-      </c>
-      <c r="AC43" t="str">
-        <v/>
-      </c>
-      <c r="AD43" t="str">
-        <v/>
-      </c>
-      <c r="AE43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="AF43" t="str">
-        <v>PS</v>
-      </c>
-      <c r="AG43" t="str">
-        <v>PT</v>
-      </c>
-      <c r="AH43" t="str">
-        <v>PT</v>
-      </c>
-      <c r="AI43">
-        <v>0</v>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>0</v>
-      </c>
-      <c r="AN43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v/>
-      </c>
-      <c r="B44" t="str">
-        <v>42791</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Nguyễn Phương Linh</v>
-      </c>
-      <c r="D44" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="E44" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="F44" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="I44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="J44" t="str">
-        <v>PS</v>
-      </c>
-      <c r="K44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="L44" t="str">
-        <v/>
-      </c>
-      <c r="M44" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="N44" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="O44" t="str">
-        <v>PT1</v>
-      </c>
-      <c r="P44" t="str">
-        <v/>
-      </c>
-      <c r="Q44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="R44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="S44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="T44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="U44" t="str">
-        <v>PS</v>
-      </c>
-      <c r="V44" t="str">
-        <v/>
-      </c>
-      <c r="W44" t="str">
-        <v/>
-      </c>
-      <c r="X44" t="str">
-        <v>PT</v>
-      </c>
-      <c r="Y44" t="str">
-        <v/>
-      </c>
-      <c r="Z44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="AA44" t="str">
-        <v>PS</v>
-      </c>
-      <c r="AB44" t="str">
-        <v/>
-      </c>
-      <c r="AC44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="AD44" t="str">
-        <v/>
-      </c>
-      <c r="AE44" t="str">
-        <v/>
-      </c>
-      <c r="AF44" t="str">
-        <v/>
-      </c>
-      <c r="AG44" t="str">
-        <v>HC</v>
-      </c>
-      <c r="AH44" t="str">
-        <v>PS1</v>
-      </c>
-      <c r="AI44">
-        <v>1</v>
-      </c>
-      <c r="AJ44">
-        <v>0</v>
-      </c>
-      <c r="AK44">
-        <v>0</v>
-      </c>
-      <c r="AL44">
-        <v>0</v>
-      </c>
-      <c r="AM44">
-        <v>0</v>
-      </c>
-      <c r="AN44">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN35"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Mục</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Giá trị</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Giờ công kế hoạch</v>
+      </c>
+      <c r="B2">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -4723,7 +4723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4735,15 +4735,23 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Công kế hoạch</v>
+      </c>
+      <c r="B2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Giờ công kế hoạch</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>216</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -3511,7 +3511,7 @@
         <v>C9</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>NC</v>
       </c>
       <c r="G26" t="str">
         <v>C9</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="AN26">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27">

--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -3770,7 +3770,7 @@
         <v>C9</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="L28" t="str">
         <v>C9</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="P28" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
         <v>E</v>
@@ -3845,10 +3845,10 @@
         <v>2</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL28">
         <v>9</v>

--- a/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
+++ b/data/2026/11.2026/Lịch trực OCD on 11-2026 web update.xlsx
@@ -3511,7 +3511,7 @@
         <v>C9</v>
       </c>
       <c r="F26" t="str">
-        <v>NC</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v>C9</v>
@@ -3523,7 +3523,7 @@
         <v>C9</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>NC</v>
       </c>
       <c r="K26" t="str">
         <v>C9</v>
@@ -3571,10 +3571,10 @@
         <v/>
       </c>
       <c r="Z26" t="str">
-        <v>E</v>
+        <v/>
       </c>
       <c r="AA26" t="str">
-        <v/>
+        <v>M</v>
       </c>
       <c r="AB26" t="str">
         <v>C9</v>
@@ -3601,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL26">
         <v>10</v>
